--- a/artfynd/S 1096-2026 artfynd.xlsx
+++ b/artfynd/S 1096-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433812</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433929</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137433931</v>
       </c>
       <c r="B4" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137436411</v>
       </c>
       <c r="B5" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137433930</v>
       </c>
       <c r="B6" t="n">
-        <v>92897</v>
+        <v>92898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137433941</v>
       </c>
       <c r="B7" t="n">
-        <v>92525</v>
+        <v>92526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137433943</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137433945</v>
       </c>
       <c r="B9" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137433932</v>
       </c>
       <c r="B10" t="n">
-        <v>79618</v>
+        <v>79619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137433944</v>
       </c>
       <c r="B11" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137433927</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>137433814</v>
       </c>
       <c r="B18" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137433815</v>
       </c>
       <c r="B19" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>137436415</v>
       </c>
       <c r="B20" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>137436427</v>
       </c>
       <c r="B21" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>137433962</v>
       </c>
       <c r="B22" t="n">
-        <v>79601</v>
+        <v>79602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137433822</v>
       </c>
       <c r="B23" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137436430</v>
       </c>
       <c r="B24" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137433949</v>
       </c>
       <c r="B25" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137433963</v>
       </c>
       <c r="B26" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>137436431</v>
       </c>
       <c r="B27" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>137433818</v>
       </c>
       <c r="B28" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137433950</v>
       </c>
       <c r="B29" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>137433820</v>
       </c>
       <c r="B30" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>137433971</v>
       </c>
       <c r="B31" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>137433972</v>
       </c>
       <c r="B32" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>137433975</v>
       </c>
       <c r="B33" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137436426</v>
       </c>
       <c r="B34" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>137433821</v>
       </c>
       <c r="B35" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>137433966</v>
       </c>
       <c r="B36" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>137433948</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>137433951</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>137436419</v>
       </c>
       <c r="B39" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>137433953</v>
       </c>
       <c r="B40" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137433964</v>
       </c>
       <c r="B41" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>137433974</v>
       </c>
       <c r="B42" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>137436418</v>
       </c>
       <c r="B43" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>137436425</v>
       </c>
       <c r="B44" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>137433955</v>
       </c>
       <c r="B45" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Elin Kannerby, Stefan Andersson</t>
+          <t>Christina Boyd, Elin Kannerby, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6141,7 +6141,7 @@
         <v>137433956</v>
       </c>
       <c r="B50" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>137433967</v>
       </c>
       <c r="B51" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/S 1096-2026 artfynd.xlsx
+++ b/artfynd/S 1096-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433812</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433929</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137433931</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137436411</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137433930</v>
       </c>
       <c r="B6" t="n">
-        <v>92898</v>
+        <v>92901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137433941</v>
       </c>
       <c r="B7" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137433943</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137433945</v>
       </c>
       <c r="B9" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137433932</v>
       </c>
       <c r="B10" t="n">
-        <v>79619</v>
+        <v>79621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137433944</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137433927</v>
       </c>
       <c r="B17" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>137433814</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137433815</v>
       </c>
       <c r="B19" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>137436415</v>
       </c>
       <c r="B20" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>137436427</v>
       </c>
       <c r="B21" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>137433962</v>
       </c>
       <c r="B22" t="n">
-        <v>79602</v>
+        <v>79604</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137433822</v>
       </c>
       <c r="B23" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137436430</v>
       </c>
       <c r="B24" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137433949</v>
       </c>
       <c r="B25" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137433963</v>
       </c>
       <c r="B26" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>137436431</v>
       </c>
       <c r="B27" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>137433818</v>
       </c>
       <c r="B28" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137433950</v>
       </c>
       <c r="B29" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>137433820</v>
       </c>
       <c r="B30" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>137433971</v>
       </c>
       <c r="B31" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>137433972</v>
       </c>
       <c r="B32" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>137433975</v>
       </c>
       <c r="B33" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137436426</v>
       </c>
       <c r="B34" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>137433821</v>
       </c>
       <c r="B35" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>137433966</v>
       </c>
       <c r="B36" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>137433948</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>137433951</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>137436419</v>
       </c>
       <c r="B39" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>137433953</v>
       </c>
       <c r="B40" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137433964</v>
       </c>
       <c r="B41" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>137433974</v>
       </c>
       <c r="B42" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>137436418</v>
       </c>
       <c r="B43" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>137436425</v>
       </c>
       <c r="B44" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>137433955</v>
       </c>
       <c r="B45" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137433956</v>
       </c>
       <c r="B50" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>137433967</v>
       </c>
       <c r="B51" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/S 1096-2026 artfynd.xlsx
+++ b/artfynd/S 1096-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433812</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433929</v>
       </c>
       <c r="B3" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137433931</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137436411</v>
       </c>
       <c r="B5" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137433930</v>
       </c>
       <c r="B6" t="n">
-        <v>92901</v>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137433941</v>
       </c>
       <c r="B7" t="n">
-        <v>92529</v>
+        <v>92533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137433943</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137433945</v>
       </c>
       <c r="B9" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137433932</v>
       </c>
       <c r="B10" t="n">
-        <v>79621</v>
+        <v>79625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137433944</v>
       </c>
       <c r="B11" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137436410</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137436412</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>137436414</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137436416</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>137433811</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137433927</v>
       </c>
       <c r="B17" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>137433814</v>
       </c>
       <c r="B18" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137433815</v>
       </c>
       <c r="B19" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>137436415</v>
       </c>
       <c r="B20" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>137436427</v>
       </c>
       <c r="B21" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>137433962</v>
       </c>
       <c r="B22" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137433822</v>
       </c>
       <c r="B23" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137436430</v>
       </c>
       <c r="B24" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137433949</v>
       </c>
       <c r="B25" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137433963</v>
       </c>
       <c r="B26" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>137436431</v>
       </c>
       <c r="B27" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>137433818</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137433950</v>
       </c>
       <c r="B29" t="n">
-        <v>92107</v>
+        <v>92111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>137433820</v>
       </c>
       <c r="B30" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>137433971</v>
       </c>
       <c r="B31" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>137433972</v>
       </c>
       <c r="B32" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>137433975</v>
       </c>
       <c r="B33" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137436426</v>
       </c>
       <c r="B34" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>137433821</v>
       </c>
       <c r="B35" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>137433966</v>
       </c>
       <c r="B36" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>137433948</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>137433951</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>137436419</v>
       </c>
       <c r="B39" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>137433953</v>
       </c>
       <c r="B40" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137433964</v>
       </c>
       <c r="B41" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>137433974</v>
       </c>
       <c r="B42" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>137436418</v>
       </c>
       <c r="B43" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>137436425</v>
       </c>
       <c r="B44" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>137433955</v>
       </c>
       <c r="B45" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>137433817</v>
       </c>
       <c r="B46" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137436422</v>
       </c>
       <c r="B47" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137436423</v>
       </c>
       <c r="B48" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>137436424</v>
       </c>
       <c r="B49" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137433956</v>
       </c>
       <c r="B50" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>137433967</v>
       </c>
       <c r="B51" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
